--- a/fixdesk-frontend/public/example/TemplateExcelUsers.xlsx
+++ b/fixdesk-frontend/public/example/TemplateExcelUsers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pachara\Team0\fixdesk-system\fixdesk-frontend\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D840777C-423E-4A81-873D-83F3777B60C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E60DB5-40FD-4525-AD3C-3D3C78D5C32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>นาย</t>
   </si>
@@ -239,6 +239,9 @@
       <t>*</t>
     </r>
   </si>
+  <si>
+    <t>หมายเหตุ: ช่องที่มีเครื่องหมาย * เป็นข้อมูลบังคับที่จำเป็นต้องระบุ</t>
+  </si>
 </sst>
 </file>
 
@@ -286,7 +289,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,17 +321,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M485"/>
+  <dimension ref="A1:R485"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="14.77734375" customWidth="1"/>
@@ -643,83 +649,88 @@
     <col min="12" max="12" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="5"/>
-    </row>
-    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="N1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+    </row>
+    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="6"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -729,7 +740,7 @@
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -755,7 +766,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -765,7 +776,7 @@
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -791,7 +802,7 @@
       </c>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -803,7 +814,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -815,7 +826,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -827,7 +838,7 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -839,7 +850,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -851,7 +862,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -863,7 +874,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -875,7 +886,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -887,7 +898,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -899,7 +910,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -911,7 +922,7 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -923,7 +934,7 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -6564,6 +6575,9 @@
       <c r="J485" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="N1:R1"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fixdesk-frontend/public/example/TemplateExcelUsers.xlsx
+++ b/fixdesk-frontend/public/example/TemplateExcelUsers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pachara\Team0\fixdesk-system\fixdesk-frontend\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E60DB5-40FD-4525-AD3C-3D3C78D5C32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A015932-2F69-435C-B4B2-B0D89DB2D5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>นาย</t>
   </si>
@@ -94,24 +94,7 @@
     </r>
   </si>
   <si>
-    <t>pass12345</t>
-  </si>
-  <si>
     <t>เจ้าหน้าที่...</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">รหัสผ่าน </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="TH SarabunPSK"/>
-        <family val="2"/>
-      </rPr>
-      <t>*</t>
-    </r>
   </si>
   <si>
     <r>
@@ -242,12 +225,42 @@
   <si>
     <t>หมายเหตุ: ช่องที่มีเครื่องหมาย * เป็นข้อมูลบังคับที่จำเป็นต้องระบุ</t>
   </si>
+  <si>
+    <t xml:space="preserve">บทบาท </t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Technician</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>ผู้ดูแลระบบ</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่ช่าง</t>
+  </si>
+  <si>
+    <t>ผู้ใช้งานทั่วไป</t>
+  </si>
+  <si>
+    <t>เจ้าหน้าที่คลัง</t>
+  </si>
+  <si>
+    <t>ผู้บริหาร</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,8 +292,15 @@
       <name val="TH SarabunPSK"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="TH SarabunPSK"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -290,6 +310,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,19 +347,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -637,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R485"/>
+  <dimension ref="A1:Q485"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="14.77734375" customWidth="1"/>
@@ -647,162 +676,167 @@
     <col min="10" max="10" width="18.77734375" customWidth="1"/>
     <col min="11" max="11" width="12.77734375" customWidth="1"/>
     <col min="12" max="12" width="14.77734375" customWidth="1"/>
+    <col min="13" max="14" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-    </row>
-    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="K2" s="2"/>
+      <c r="M2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="K3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="K4" s="2"/>
+      <c r="M4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -813,8 +847,14 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="M5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -825,8 +865,14 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="M6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -837,8 +883,14 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="M7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -850,7 +902,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -862,7 +914,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -874,7 +926,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -886,7 +938,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -898,7 +950,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -910,7 +962,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -922,7 +974,7 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -934,7 +986,7 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -6575,8 +6627,9 @@
       <c r="J485" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="N1:R1"/>
+  <mergeCells count="2">
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="M2:N2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
